--- a/exemplos/modelo-experimento-doe.xlsx
+++ b/exemplos/modelo-experimento-doe.xlsx
@@ -760,7 +760,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -811,14 +811,25 @@
         <v>Se "sim", alguns ensaios podem pedir valores um pouco além do mínimo/máximo informado</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Grau do modelo</v>
+      </c>
+      <c r="B5" t="str">
+        <v>simples</v>
+      </c>
+      <c r="C5" t="str">
+        <v>"simples" é a curva padrão. "cubico" descreve curvas em S nos mesmos ensaios — só funciona com "Tipo de planejamento" diferente de "face". "cubico completo" pede vários ensaios a mais.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>Estas opções já estão nos valores recomendados. Se você não sabe o que são, não mude.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>